--- a/NECP Scenario/Results/Regional Results/EL54_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL54_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176539102754377E-11</v>
+        <v>1.737115892811593E-11</v>
       </c>
       <c r="C2">
-        <v>6.160907469753047E-12</v>
+        <v>9.096362403936898E-12</v>
       </c>
       <c r="D2">
-        <v>9.052350605943854E-12</v>
+        <v>1.336546791408849E-11</v>
       </c>
       <c r="E2">
-        <v>1.330097795204049E-11</v>
+        <v>1.963839931455804E-11</v>
       </c>
       <c r="F2">
-        <v>1.954356282034512E-11</v>
+        <v>2.885532104114816E-11</v>
       </c>
       <c r="G2">
-        <v>2.871582258589385E-11</v>
+        <v>4.239780704190269E-11</v>
       </c>
       <c r="H2">
-        <v>1.740395459605835E-10</v>
+        <v>2.569629317918943E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.542473687961951E-08</v>
+        <v>3.774166488211965E-08</v>
       </c>
       <c r="C3">
-        <v>2.550602355438927E-08</v>
+        <v>3.786351076609508E-08</v>
       </c>
       <c r="D3">
-        <v>5.656797813585113E-08</v>
+        <v>8.269480722720809E-08</v>
       </c>
       <c r="E3">
-        <v>1.121123552477486E-07</v>
+        <v>1.571262646686189E-07</v>
       </c>
       <c r="F3">
-        <v>3.438432925700367E-07</v>
+        <v>4.466625626833696E-07</v>
       </c>
       <c r="G3">
-        <v>1.292127359039482E-06</v>
+        <v>1.84639830349092E-06</v>
       </c>
       <c r="H3">
-        <v>0.9460327930806972</v>
+        <v>0.6103262556248124</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0442367653263323</v>
+        <v>0.0442287902384337</v>
       </c>
       <c r="D4">
-        <v>0.0442367653459045</v>
+        <v>0.0442287902694874</v>
       </c>
       <c r="E4">
-        <v>0.0493378127117777</v>
+        <v>0.0490282100766809</v>
       </c>
       <c r="F4">
-        <v>0.0521625867048371</v>
+        <v>0.0523479708854344</v>
       </c>
       <c r="G4">
-        <v>0.0553614654082605</v>
+        <v>0.0554307331380003</v>
       </c>
       <c r="H4">
-        <v>0.0589517667299806</v>
+        <v>0.0591042018174718</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>2.016881791712227E-08</v>
+        <v>2.961692221058944E-08</v>
       </c>
       <c r="D9">
-        <v>2.342039723992318E-08</v>
+        <v>3.584538519702487E-08</v>
       </c>
       <c r="E9">
-        <v>2.542245624753569E-08</v>
+        <v>3.804763913037759E-08</v>
       </c>
       <c r="F9">
-        <v>2.545482502998517E-08</v>
+        <v>3.809155209180901E-08</v>
       </c>
       <c r="G9">
-        <v>2.55023770336393E-08</v>
+        <v>3.816114246281581E-08</v>
       </c>
       <c r="H9">
-        <v>1.276923748271997E-07</v>
+        <v>1.888715325687473E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.6671363600052406</v>
+        <v>0.6671363600057172</v>
       </c>
       <c r="C13">
-        <v>0.6671363600069697</v>
+        <v>0.6671363600082592</v>
       </c>
       <c r="D13">
-        <v>0.6671363600112423</v>
+        <v>0.6671363600137139</v>
       </c>
       <c r="E13">
-        <v>0.6671363600191842</v>
+        <v>0.6671363600233247</v>
       </c>
       <c r="F13">
-        <v>0.6671363600340472</v>
+        <v>0.6671363600421493</v>
       </c>
       <c r="G13">
-        <v>0.6671363600624575</v>
+        <v>0.6671363600792758</v>
       </c>
       <c r="H13">
-        <v>0.667136360352891</v>
+        <v>0.6671363604218509</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.816226637122187E-08</v>
+        <v>2.687106035660596E-08</v>
       </c>
       <c r="C18">
-        <v>1.817349138515992E-08</v>
+        <v>2.688785917904416E-08</v>
       </c>
       <c r="D18">
-        <v>3.483144448539596E-08</v>
+        <v>5.216559253513696E-08</v>
       </c>
       <c r="E18">
-        <v>7.666259332438459E-08</v>
+        <v>1.10931877935361E-07</v>
       </c>
       <c r="F18">
-        <v>2.237985772595556E-07</v>
+        <v>3.023461661355796E-07</v>
       </c>
       <c r="G18">
-        <v>3.774016188003309E-07</v>
+        <v>5.663341122597747E-07</v>
       </c>
       <c r="H18">
-        <v>2.97136512391925E-06</v>
+        <v>4.381631591286747E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -952,22 +952,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>1.050396060206228E-08</v>
+        <v>1.563281898914208E-08</v>
       </c>
       <c r="D19">
-        <v>1.561981509819412E-08</v>
+        <v>2.420165473672282E-08</v>
       </c>
       <c r="E19">
-        <v>3.919262959413393E-08</v>
+        <v>6.178957412415334E-08</v>
       </c>
       <c r="F19">
-        <v>2.014043847738361E-07</v>
+        <v>2.697535678515102E-07</v>
       </c>
       <c r="G19">
-        <v>0.1658824211802671</v>
+        <v>0.1746877890120766</v>
       </c>
       <c r="H19">
-        <v>0.3314339117667849</v>
+        <v>0.3314339116538229</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.915790960422513E-08</v>
+        <v>4.311883813957108E-08</v>
       </c>
       <c r="C22">
-        <v>2.917488626976613E-08</v>
+        <v>4.314395732917974E-08</v>
       </c>
       <c r="D22">
-        <v>2.933253625909146E-08</v>
+        <v>4.3382272578685E-08</v>
       </c>
       <c r="E22">
-        <v>4.047396851298707E-08</v>
+        <v>5.994946336765689E-08</v>
       </c>
       <c r="F22">
-        <v>5.809383997899673E-08</v>
+        <v>8.580661923720749E-08</v>
       </c>
       <c r="G22">
-        <v>8.387112599209512E-08</v>
+        <v>1.242764395398631E-07</v>
       </c>
       <c r="H22">
-        <v>5.147021591027912E-07</v>
+        <v>7.604329394896818E-07</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>4.920339812005722E-09</v>
+        <v>7.266370840090008E-09</v>
       </c>
       <c r="D24">
-        <v>1.601427637384785E-08</v>
+        <v>2.400504675260465E-08</v>
       </c>
       <c r="E24">
-        <v>4.476901917063473E-08</v>
+        <v>6.713927719290416E-08</v>
       </c>
       <c r="F24">
-        <v>1.308938310571202E-07</v>
+        <v>1.939920936936848E-07</v>
       </c>
       <c r="G24">
-        <v>3.44269849408346E-07</v>
+        <v>6.244229603645967E-07</v>
       </c>
       <c r="H24">
-        <v>0.4266081023216579</v>
+        <v>0.6317881053081295</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.1581072941141425</v>
+        <v>0.1135915403440229</v>
       </c>
       <c r="D27">
-        <v>0.2963406282569405</v>
+        <v>0.248178592282619</v>
       </c>
       <c r="E27">
-        <v>0.3582660739526512</v>
+        <v>0.3034739652715302</v>
       </c>
       <c r="F27">
-        <v>0.4587128617726887</v>
+        <v>0.3930364854849902</v>
       </c>
       <c r="G27">
-        <v>0.8267784799822901</v>
+        <v>0.7563676183108401</v>
       </c>
       <c r="H27">
-        <v>2.25193229700888</v>
+        <v>1.936875562423737</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>8.494288457726896E-09</v>
+        <v>1.261716398017738E-08</v>
       </c>
       <c r="D29">
-        <v>3.088844094099446E-08</v>
+        <v>4.926445929086793E-08</v>
       </c>
       <c r="E29">
-        <v>1.59169895103296E-07</v>
+        <v>4.568685913194773E-07</v>
       </c>
       <c r="F29">
-        <v>0.2866423042965247</v>
+        <v>0.3015805374917782</v>
       </c>
       <c r="G29">
-        <v>0.4502106790159886</v>
+        <v>0.4664015015076269</v>
       </c>
       <c r="H29">
-        <v>0.7861770806804007</v>
+        <v>0.810067228318043</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1.017430202840216E-08</v>
+        <v>1.499758814762063E-08</v>
       </c>
       <c r="D31">
-        <v>1.117969636349859E-08</v>
+        <v>1.681379899887228E-08</v>
       </c>
       <c r="E31">
-        <v>2.333851322865274E-08</v>
+        <v>3.477113056878173E-08</v>
       </c>
       <c r="F31">
-        <v>4.288161650495741E-08</v>
+        <v>6.31803048858834E-08</v>
       </c>
       <c r="G31">
-        <v>5.725860803737038E-08</v>
+        <v>8.5894734570864E-08</v>
       </c>
       <c r="H31">
-        <v>3.501617020181612E-07</v>
+        <v>5.223800782469162E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>2.915890972266863E-08</v>
+        <v>4.280081914754704E-08</v>
       </c>
       <c r="D33">
-        <v>3.606544694524189E-08</v>
+        <v>5.416631465985389E-08</v>
       </c>
       <c r="E33">
-        <v>1.068912828764037E-07</v>
+        <v>1.587369252907132E-07</v>
       </c>
       <c r="F33">
-        <v>1.45271940218798E-07</v>
+        <v>2.187237195835691E-07</v>
       </c>
       <c r="G33">
-        <v>1.474096744131314E-07</v>
+        <v>2.253509485348813E-07</v>
       </c>
       <c r="H33">
-        <v>7.386676279261986E-07</v>
+        <v>1.094818899665252E-06</v>
       </c>
     </row>
     <row r="34" spans="1:8">
